--- a/Assets/Data/Units.xlsx
+++ b/Assets/Data/Units.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Medewerker\Dropbox\Werk\Lessen\Game Dev Git Gud Coding Standards\Code Examples\CodeExample\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40970E69-788D-49E2-AC70-4F582C3812DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17BDACC3-28EC-481E-ABD3-EE4170558E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{CAFAB463-81FD-4DEF-8CAD-0191B5E2E3CE}"/>
+    <workbookView xWindow="2196" yWindow="2196" windowWidth="17280" windowHeight="9960" xr2:uid="{CAFAB463-81FD-4DEF-8CAD-0191B5E2E3CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="1" r:id="rId1"/>
@@ -428,15 +428,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37F309F1-1DA5-4455-9119-BFF2100904BA}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -453,7 +453,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -470,7 +470,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -487,7 +487,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -504,7 +504,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -521,7 +521,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -538,7 +538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
